--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R2" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +757,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,45 +812,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R3" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,40 +883,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,20 +934,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,26 +955,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R4" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,19 +1003,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,12 +1020,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1119,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606008</v>
+        <v>124616298</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,51 +1150,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575385</v>
+        <v>575565</v>
       </c>
       <c r="R6" t="n">
-        <v>6387661</v>
+        <v>6387597</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,39 +1215,30 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R2" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +756,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606008</v>
+        <v>124607679</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,48 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575385</v>
+        <v>575590</v>
       </c>
       <c r="R3" t="n">
-        <v>6387661</v>
+        <v>6387628</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,19 +858,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,20 +899,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,25 +920,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R4" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,9 +969,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124607679</v>
+        <v>124606008</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,34 +1024,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575590</v>
+        <v>575385</v>
       </c>
       <c r="R5" t="n">
-        <v>6387628</v>
+        <v>6387661</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,9 +1095,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,12 +1122,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R2" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +757,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124607679</v>
+        <v>124616298</v>
       </c>
       <c r="B3" t="n">
         <v>106461</v>
@@ -818,20 +829,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575590</v>
+        <v>575565</v>
       </c>
       <c r="R3" t="n">
-        <v>6387628</v>
+        <v>6387597</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,17 +900,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124606505</v>
+        <v>124606008</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,24 +945,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575499</v>
+        <v>575385</v>
       </c>
       <c r="R4" t="n">
-        <v>6387623</v>
+        <v>6387661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,17 +1026,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606008</v>
+        <v>124616273</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,37 +1045,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1058,17 +1077,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575385</v>
+        <v>575636</v>
       </c>
       <c r="R5" t="n">
-        <v>6387661</v>
+        <v>6387668</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,19 +1114,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,19 +1131,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124616298</v>
+        <v>124607679</v>
       </c>
       <c r="B6" t="n">
         <v>106461</v>
@@ -1167,28 +1176,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575565</v>
+        <v>575590</v>
       </c>
       <c r="R6" t="n">
-        <v>6387597</v>
+        <v>6387628</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1227,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R2" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +756,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,45 +801,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R3" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,40 +872,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124606008</v>
+        <v>124616298</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,51 +927,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575385</v>
+        <v>575565</v>
       </c>
       <c r="R4" t="n">
-        <v>6387661</v>
+        <v>6387597</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,49 +992,40 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616273</v>
+        <v>124607679</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,49 +1034,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575636</v>
+        <v>575590</v>
       </c>
       <c r="R5" t="n">
-        <v>6387668</v>
+        <v>6387628</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,17 +1117,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124607679</v>
+        <v>124606505</v>
       </c>
       <c r="B6" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,37 +1140,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575590</v>
+        <v>575499</v>
       </c>
       <c r="R6" t="n">
-        <v>6387628</v>
+        <v>6387623</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,9 +1206,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616273</v>
+        <v>124606008</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -719,17 +725,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575636</v>
+        <v>575385</v>
       </c>
       <c r="R2" t="n">
-        <v>6387668</v>
+        <v>6387661</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,9 +762,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606008</v>
+        <v>124607679</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,48 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575385</v>
+        <v>575590</v>
       </c>
       <c r="R3" t="n">
-        <v>6387661</v>
+        <v>6387628</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,19 +874,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616298</v>
+        <v>124606505</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,42 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575565</v>
+        <v>575499</v>
       </c>
       <c r="R4" t="n">
-        <v>6387597</v>
+        <v>6387623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,37 +985,46 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124607679</v>
+        <v>124616298</v>
       </c>
       <c r="B5" t="n">
         <v>106461</v>
@@ -1055,20 +1057,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575590</v>
+        <v>575565</v>
       </c>
       <c r="R5" t="n">
-        <v>6387628</v>
+        <v>6387597</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,6 +1116,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,17 +1128,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,26 +1168,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R6" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1216,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606008</v>
+        <v>124616298</v>
       </c>
       <c r="B2" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575385</v>
+        <v>575565</v>
       </c>
       <c r="R2" t="n">
-        <v>6387661</v>
+        <v>6387597</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,39 +756,30 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1024,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,45 +1025,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R5" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,30 +1096,39 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124607679</v>
+        <v>124606505</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +802,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575590</v>
+        <v>575499</v>
       </c>
       <c r="R3" t="n">
-        <v>6387628</v>
+        <v>6387623</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,9 +868,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124606505</v>
+        <v>124607679</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,46 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575499</v>
+        <v>575590</v>
       </c>
       <c r="R4" t="n">
-        <v>6387623</v>
+        <v>6387628</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,19 +980,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606008</v>
+        <v>124616273</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,37 +1021,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1059,17 +1053,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575385</v>
+        <v>575636</v>
       </c>
       <c r="R5" t="n">
-        <v>6387661</v>
+        <v>6387668</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1090,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1107,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Viveka Berg, Moritz Moser, Ingrid Runeson, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124616273</v>
+        <v>124606008</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,31 +1131,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1179,17 +1169,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575636</v>
+        <v>575385</v>
       </c>
       <c r="R6" t="n">
-        <v>6387668</v>
+        <v>6387661</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,9 +1206,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B2" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R2" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,40 +762,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,26 +834,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R3" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +882,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,19 +899,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124607679</v>
+        <v>124616298</v>
       </c>
       <c r="B4" t="n">
         <v>106461</v>
@@ -940,20 +944,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575590</v>
+        <v>575565</v>
       </c>
       <c r="R4" t="n">
-        <v>6387628</v>
+        <v>6387597</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +1003,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,17 +1015,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616273</v>
+        <v>124607679</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,49 +1034,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575636</v>
+        <v>575590</v>
       </c>
       <c r="R5" t="n">
-        <v>6387668</v>
+        <v>6387628</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,17 +1117,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viveka Berg, Moritz Moser, Ingrid Runeson, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606008</v>
+        <v>124606505</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,29 +1162,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575385</v>
+        <v>575499</v>
       </c>
       <c r="R6" t="n">
-        <v>6387661</v>
+        <v>6387623</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606008</v>
+        <v>124607679</v>
       </c>
       <c r="B2" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575385</v>
+        <v>575590</v>
       </c>
       <c r="R2" t="n">
-        <v>6387661</v>
+        <v>6387628</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +748,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616273</v>
+        <v>124616298</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,46 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575636</v>
+        <v>575565</v>
       </c>
       <c r="R3" t="n">
-        <v>6387668</v>
+        <v>6387597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616298</v>
+        <v>124616273</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,46 +900,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575565</v>
+        <v>575636</v>
       </c>
       <c r="R4" t="n">
-        <v>6387597</v>
+        <v>6387668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124607679</v>
+        <v>124606505</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,37 +1014,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575590</v>
+        <v>575499</v>
       </c>
       <c r="R5" t="n">
-        <v>6387628</v>
+        <v>6387623</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,9 +1080,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1107,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606505</v>
+        <v>124606008</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>98018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,24 +1157,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575499</v>
+        <v>575385</v>
       </c>
       <c r="R6" t="n">
-        <v>6387623</v>
+        <v>6387661</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124607679</v>
+        <v>124606505</v>
       </c>
       <c r="B2" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575590</v>
+        <v>575499</v>
       </c>
       <c r="R2" t="n">
-        <v>6387628</v>
+        <v>6387623</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +757,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +784,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -888,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616273</v>
+        <v>124607679</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,49 +919,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575636</v>
+        <v>575590</v>
       </c>
       <c r="R4" t="n">
-        <v>6387668</v>
+        <v>6387628</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,17 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,26 +1042,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R5" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,19 +1090,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,12 +1107,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R2" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +756,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616298</v>
+        <v>124606505</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,42 +801,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575565</v>
+        <v>575499</v>
       </c>
       <c r="R3" t="n">
-        <v>6387597</v>
+        <v>6387623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,37 +867,46 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124607679</v>
+        <v>124616298</v>
       </c>
       <c r="B4" t="n">
         <v>106461</v>
@@ -940,20 +939,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575590</v>
+        <v>575565</v>
       </c>
       <c r="R4" t="n">
-        <v>6387628</v>
+        <v>6387597</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,17 +1010,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616273</v>
+        <v>124606008</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,31 +1029,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1053,17 +1067,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575636</v>
+        <v>575385</v>
       </c>
       <c r="R5" t="n">
-        <v>6387668</v>
+        <v>6387661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,9 +1104,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606008</v>
+        <v>124607679</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,48 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575385</v>
+        <v>575590</v>
       </c>
       <c r="R6" t="n">
-        <v>6387661</v>
+        <v>6387628</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,19 +1216,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R2" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +757,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606505</v>
+        <v>124606008</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,24 +834,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575499</v>
+        <v>575385</v>
       </c>
       <c r="R3" t="n">
-        <v>6387623</v>
+        <v>6387661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1017,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606008</v>
+        <v>124616273</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1045,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1067,17 +1077,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575385</v>
+        <v>575636</v>
       </c>
       <c r="R5" t="n">
-        <v>6387661</v>
+        <v>6387668</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,19 +1114,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606505</v>
+        <v>124607679</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575499</v>
+        <v>575590</v>
       </c>
       <c r="R2" t="n">
-        <v>6387623</v>
+        <v>6387628</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,19 +748,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606008</v>
+        <v>124616273</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -846,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575385</v>
+        <v>575636</v>
       </c>
       <c r="R3" t="n">
-        <v>6387661</v>
+        <v>6387668</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,19 +858,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Viveka Berg, Moritz Moser, Ingrid Runeson, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,45 +903,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R4" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,40 +974,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,20 +1025,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,25 +1046,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R5" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,9 +1095,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,19 +1122,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124607679</v>
+        <v>124616298</v>
       </c>
       <c r="B6" t="n">
         <v>106461</v>
@@ -1176,20 +1167,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575590</v>
+        <v>575565</v>
       </c>
       <c r="R6" t="n">
-        <v>6387628</v>
+        <v>6387597</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,6 +1226,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124607679</v>
+        <v>124606008</v>
       </c>
       <c r="B2" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575590</v>
+        <v>575385</v>
       </c>
       <c r="R2" t="n">
-        <v>6387628</v>
+        <v>6387661</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,9 +762,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616273</v>
+        <v>124616298</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +813,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575636</v>
+        <v>575565</v>
       </c>
       <c r="R3" t="n">
-        <v>6387668</v>
+        <v>6387597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,17 +905,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viveka Berg, Moritz Moser, Ingrid Runeson, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124606008</v>
+        <v>124616273</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,37 +924,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -937,17 +956,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575385</v>
+        <v>575636</v>
       </c>
       <c r="R4" t="n">
-        <v>6387661</v>
+        <v>6387668</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +993,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,12 +1010,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1127,14 +1136,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124616298</v>
+        <v>124607679</v>
       </c>
       <c r="B6" t="n">
         <v>106461</v>
@@ -1167,28 +1176,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575565</v>
+        <v>575590</v>
       </c>
       <c r="R6" t="n">
-        <v>6387597</v>
+        <v>6387628</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1227,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124606008</v>
+        <v>124616298</v>
       </c>
       <c r="B2" t="n">
-        <v>98018</v>
+        <v>106461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575385</v>
+        <v>575565</v>
       </c>
       <c r="R2" t="n">
-        <v>6387661</v>
+        <v>6387597</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,49 +756,40 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616298</v>
+        <v>124606505</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,42 +802,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575565</v>
+        <v>575499</v>
       </c>
       <c r="R3" t="n">
-        <v>6387597</v>
+        <v>6387623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,40 +868,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616273</v>
+        <v>124607679</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,49 +919,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575636</v>
+        <v>575590</v>
       </c>
       <c r="R4" t="n">
-        <v>6387668</v>
+        <v>6387628</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,17 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606505</v>
+        <v>124616273</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,26 +1042,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575499</v>
+        <v>575636</v>
       </c>
       <c r="R5" t="n">
-        <v>6387623</v>
+        <v>6387668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,19 +1090,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1107,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124607679</v>
+        <v>124606008</v>
       </c>
       <c r="B6" t="n">
-        <v>106461</v>
+        <v>98018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1135,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575590</v>
+        <v>575385</v>
       </c>
       <c r="R6" t="n">
-        <v>6387628</v>
+        <v>6387661</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,9 +1206,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616298</v>
+        <v>124616273</v>
       </c>
       <c r="B2" t="n">
-        <v>106461</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575565</v>
+        <v>575636</v>
       </c>
       <c r="R2" t="n">
-        <v>6387597</v>
+        <v>6387668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606505</v>
+        <v>124616298</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,43 +801,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575499</v>
+        <v>575565</v>
       </c>
       <c r="R3" t="n">
-        <v>6387623</v>
+        <v>6387597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,39 +866,30 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1009,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616273</v>
+        <v>124606008</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,31 +1010,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1053,17 +1048,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575636</v>
+        <v>575385</v>
       </c>
       <c r="R5" t="n">
-        <v>6387668</v>
+        <v>6387661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,9 +1085,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,22 +1112,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606008</v>
+        <v>124606505</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,29 +1162,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575385</v>
+        <v>575499</v>
       </c>
       <c r="R6" t="n">
-        <v>6387661</v>
+        <v>6387623</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 18164-2025 artfynd.xlsx
+++ b/artfynd/A 18164-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124616273</v>
+        <v>124606505</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Sm</t>
+          <t>Kungsfågel, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575636</v>
+        <v>575499</v>
       </c>
       <c r="R2" t="n">
-        <v>6387668</v>
+        <v>6387623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +757,19 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124616298</v>
+        <v>124606008</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>98186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,45 +812,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13, Sm</t>
+          <t>Fläcknycklar, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575565</v>
+        <v>575385</v>
       </c>
       <c r="R3" t="n">
-        <v>6387597</v>
+        <v>6387661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,40 +883,49 @@
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Moritz Moser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
+          <t>Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124607679</v>
+        <v>124616273</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,41 +934,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Virveln, Sm</t>
+          <t>2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575590</v>
+        <v>575636</v>
       </c>
       <c r="R4" t="n">
-        <v>6387628</v>
+        <v>6387668</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,17 +1025,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124606008</v>
+        <v>124616298</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>106640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,51 +1048,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fläcknycklar, Sm</t>
+          <t>13, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575385</v>
+        <v>575565</v>
       </c>
       <c r="R5" t="n">
-        <v>6387661</v>
+        <v>6387597</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,49 +1113,40 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Ingrid Runeson, Moritz Moser, Viveka Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124606505</v>
+        <v>124607679</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>106640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,46 +1159,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kungsfågel, Sm</t>
+          <t>Virveln, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575499</v>
+        <v>575590</v>
       </c>
       <c r="R6" t="n">
-        <v>6387623</v>
+        <v>6387628</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,19 +1216,9 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moritz Moser</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Viveka Berg, Ingrid Runeson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
